--- a/out/MLP-mamba2_repeat_3_000006.xlsx
+++ b/out/MLP-mamba2_repeat_3_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.566666627777779</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.349999978125</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.349999978125</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.566666627777779</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.166666627777778</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.349999978125</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.349999978125</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.166666627777778</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.166666627777778</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.7499999781250004</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.166666627777778</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.166666627777778</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.166666627777778</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.166666627777778</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7499999781250004</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.566666627777779</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.349999978125</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.566666627777779</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.349999978125</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7499999781250004</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.166666627777778</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7499999781250004</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.349999978125</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.166666627777778</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.166666627777778</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.166666627777778</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003487098065717146</v>
+        <v>-0.0003379785206309752</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4488164737823076</v>
+        <v>0.4350046833118248</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8984827461107256</v>
+        <v>0.8708326047338792</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1036502688119408</v>
+        <v>-0.1004604614743699</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3448174951637951</v>
+        <v>0.3342062433168241</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.566666627777779</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3448174951637951</v>
+        <v>0.3342062433168241</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.166666627777778</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3444374614015748</v>
+        <v>0.333907182069146</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.167545907184956</v>
+        <v>0.9187808306399052</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.681854132560778</v>
+        <v>2.173298350727501</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2233967538369425</v>
+        <v>0.1757983594387689</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.166666627777778</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.959397928290881</v>
+        <v>1.604773458151353</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.3913006008667315</v>
+        <v>0.3079274989375442</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.566666627777779</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.51871188355817</v>
+        <v>2.044916271591547</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.2142904486965833</v>
+        <v>0.1686323040833162</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.555654902609721</v>
+        <v>2.073987965922067</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.08850487927373304</v>
+        <v>0.0696475974271141</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.166666627777778</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.518149963269384</v>
+        <v>2.044474077472193</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1102699750181405</v>
+        <v>0.08677492964006694</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.166666627777778</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.650199495623036</v>
+        <v>2.148388029362604</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.06639676879452934</v>
+        <v>0.05224971656632046</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.672648229079838</v>
+        <v>2.166053647459481</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.05047939361115884</v>
+        <v>0.03972293277229061</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.166666627777778</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.70718187535607</v>
+        <v>2.19322926695927</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02232716716278827</v>
+        <v>0.01757035093241838</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.166666627777778</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.701312294182706</v>
+        <v>2.188610203542475</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01771551456641843</v>
+        <v>0.01394030911547999</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.166666627777778</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.714410638516507</v>
+        <v>2.198917302302507</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.008782700164990628</v>
+        <v>0.006911592928038455</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.166666627777778</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.714248779122181</v>
+        <v>2.198788858284942</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.005106465710071104</v>
+        <v>0.004015515430460025</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.166666627777778</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.715671866118549</v>
+        <v>2.199907554047343</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002549278254662737</v>
+        <v>0.002005257715230013</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.715663685869695</v>
+        <v>2.199900051140785</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001256970543285567</v>
+        <v>0.0009896282641840691</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.715626705758909</v>
+        <v>2.199869873125353</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.000729283611138602</v>
+        <v>0.0005724139305771735</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.715824762429365</v>
+        <v>2.200024549507121</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002405167125369099</v>
+        <v>0.0001869494298015841</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.715575911057578</v>
+        <v>2.199827795059919</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001185185130999074</v>
+        <v>9.156901933265487e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.715572277817124</v>
+        <v>2.199823877455022</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>6.104729551292968e-05</v>
+        <v>4.881631486238714e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.715578230555088</v>
+        <v>2.199827638419042</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.818252625748566e-05</v>
+        <v>2.107198491659588e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.566666627777779</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.715571057915067</v>
+        <v>2.199820931344739</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.536440521940679e-05</v>
+        <v>9.546003728147707e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.715573587910609</v>
+        <v>2.199821849580883</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.715566253516466</v>
+        <v>2.199814847290063</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.166666627777778</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.715562768296158</v>
+        <v>2.199810985214967</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.715558220983972</v>
+        <v>2.199806437902782</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.715558310928622</v>
+        <v>2.199806527847432</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.715557452995037</v>
+        <v>2.199805669913847</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.715557681316072</v>
+        <v>2.199805898234882</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.715556885651861</v>
+        <v>2.19980510257067</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.715556947921233</v>
+        <v>2.199805164840043</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.715556975596511</v>
+        <v>2.19980519251532</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.349999978125</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.715557127810533</v>
+        <v>2.199805344729342</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.715556781869572</v>
+        <v>2.199804998788381</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.715556857976583</v>
+        <v>2.199805074895393</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.715557024028245</v>
+        <v>2.199805240947054</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.166666627777778</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.715557383806845</v>
+        <v>2.199805600725654</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.166666627777778</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.715557404563303</v>
+        <v>2.199805621482112</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.166666627777778</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.715557508345591</v>
+        <v>2.1998057252644</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.715557736666626</v>
+        <v>2.199805953585435</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.715557612127879</v>
+        <v>2.199805829046689</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.715557639803157</v>
+        <v>2.199805856721966</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.566666627777779</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.715557695153711</v>
+        <v>2.19980591207252</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.715557958068841</v>
+        <v>2.19980617498765</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.71555787504301</v>
+        <v>2.19980609196182</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.715557667478433</v>
+        <v>2.199805884397243</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.715557681316072</v>
+        <v>2.199805898234882</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.715557819692457</v>
+        <v>2.199806036611266</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.715557536020868</v>
+        <v>2.199805752939677</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.715557363050387</v>
+        <v>2.199805579969197</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.166666627777778</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.715557259268099</v>
+        <v>2.199805476186908</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.715557404563303</v>
+        <v>2.199805621482112</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.715557646721976</v>
+        <v>2.199805863640785</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.715557473751495</v>
+        <v>2.199805690670305</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.715557176242268</v>
+        <v>2.199805393161077</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.715557162404629</v>
+        <v>2.199805379323439</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.71555679570721</v>
+        <v>2.199805012626019</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.166666627777778</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.71555679570721</v>
+        <v>2.199805012626019</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.715556733437837</v>
+        <v>2.199804950356647</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.715556629655548</v>
+        <v>2.199804846574358</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.715556456685067</v>
+        <v>2.199804673603877</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.715556505116802</v>
+        <v>2.199804722035612</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.715556145338202</v>
+        <v>2.199804362257012</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.166666627777778</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.715556103825287</v>
+        <v>2.199804320744096</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>2.166666627777778</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.715556159175841</v>
+        <v>2.19980437609465</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.715556214526395</v>
+        <v>2.199804431445204</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.71555625603931</v>
+        <v>2.19980447295812</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.71555598620536</v>
+        <v>2.199804203124169</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.166666627777778</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.715556041555914</v>
+        <v>2.199804258474723</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.715556186851118</v>
+        <v>2.199804403769927</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.715556152257022</v>
+        <v>2.199804369175831</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.715556138419383</v>
+        <v>2.199804355338193</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.166666627777778</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.715556228364033</v>
+        <v>2.199804445282842</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.166666627777778</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.715556546629718</v>
+        <v>2.199804763548527</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.715556366740417</v>
+        <v>2.199804583659227</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.715556408253333</v>
+        <v>2.199804625172142</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.715556221445214</v>
+        <v>2.199804438364023</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.715556290633406</v>
+        <v>2.199804507552215</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.715556089987649</v>
+        <v>2.199804306906458</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.715556131500564</v>
+        <v>2.199804348419373</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.166666627777778</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.715556159175841</v>
+        <v>2.19980437609465</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_3_000006.xlsx
+++ b/out/MLP-mamba2_repeat_3_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.566666627777779</v>
+        <v>0.2399999941666668</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.349999978125</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.349999978125</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.166666627777778</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.349999978125</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7499999781250004</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-0.5599999850000004</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.349999978125</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.166666627777778</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.7499999781250004</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.166666627777778</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7499999781250004</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7499999781250004</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.166666627777778</v>
+        <v>0.773333320555556</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7499999781250004</v>
+        <v>0.1066666677777779</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7499999781250004</v>
+        <v>0.1066666677777779</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.09333333222222216</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222216</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222209</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.09333333222222212</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222212</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7499999781250004</v>
+        <v>0.1066666677777779</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.166666627777778</v>
+        <v>0.1066666677777779</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7499999781250004</v>
+        <v>0.1066666677777779</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222209</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555561</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555561</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003487098065717146</v>
+        <v>-0.0001887703624767018</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4488164737823076</v>
+        <v>0.2429621610111188</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.7499999781250004</v>
+        <v>0.1066666677777779</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8984827461107256</v>
+        <v>0.4863841233024567</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1036502688119408</v>
+        <v>-0.05610994950711986</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.349999978125</v>
+        <v>0.1066666677777779</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3448174951637951</v>
+        <v>0.1866634411415223</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.566666627777779</v>
+        <v>0.5733333205555561</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3448174951637951</v>
+        <v>0.1866634411415223</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555561</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3444374614015748</v>
+        <v>0.1864674386832332</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.167545907184956</v>
+        <v>0.602161941182098</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7499999781250004</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.681854132560778</v>
+        <v>1.391990366214386</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2233967538369425</v>
+        <v>0.115216902493002</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.959397928290881</v>
+        <v>1.01938349251028</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.3913006008667315</v>
+        <v>0.2018131141307353</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.566666627777779</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.51871188355817</v>
+        <v>1.307849732197781</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.2142904486965833</v>
+        <v>0.1105202053974328</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7499999781250004</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.555654902609721</v>
+        <v>1.326903119664346</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.08850487927373304</v>
+        <v>0.04564645436665134</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.518149963269384</v>
+        <v>1.307559880347741</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1102699750181405</v>
+        <v>0.05687205544613995</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.650199495623036</v>
+        <v>1.375664804869744</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.06639676879452934</v>
+        <v>0.03424373308407815</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.672648229079838</v>
+        <v>1.387242804413356</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.05047939361115884</v>
+        <v>0.02603534084492132</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.70718187535607</v>
+        <v>1.405053938563369</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02232716716278827</v>
+        <v>0.0115141888911942</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.701312294182706</v>
+        <v>1.402025322933078</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01771551456641843</v>
+        <v>0.009135495611231592</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.714410638516507</v>
+        <v>1.408778807458894</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.008782700164990628</v>
+        <v>0.004527682237108746</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.714248779122181</v>
+        <v>1.408692910330566</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.005106465710071104</v>
+        <v>0.002630735875540364</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.715671866118549</v>
+        <v>1.409424305787999</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002549278254662737</v>
+        <v>0.001312867937770182</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222231</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.715663685869695</v>
+        <v>1.409417664953453</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001256970543285567</v>
+        <v>0.0006446704846982648</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.715626705758909</v>
+        <v>1.409396184603613</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.000729283611138602</v>
+        <v>0.0003721547639030092</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.715824762429365</v>
+        <v>1.409495945454327</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002405167125369099</v>
+        <v>0.0001222222964963988</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.715575911057578</v>
+        <v>1.409364586107127</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001185185130999074</v>
+        <v>5.788215212358921e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.715572277817124</v>
+        <v>1.409360295749626</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>6.104729551292968e-05</v>
+        <v>2.924674582151908e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222231</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.715578230555088</v>
+        <v>1.409361071554305</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.818252625748566e-05</v>
+        <v>1.159126312874283e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.09333333222222231</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.715571057915067</v>
+        <v>1.409354909127283</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.536440521940679e-05</v>
+        <v>6.636802982518164e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7499999781250004</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.715573587910609</v>
+        <v>1.40935421198188</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.732487839350877e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.715566253516466</v>
+        <v>1.409347877121332</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.715562768296158</v>
+        <v>1.409343634511178</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7499999781250004</v>
+        <v>0.1066666677777777</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.715558220983972</v>
+        <v>1.409343862832213</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-0.5599999850000004</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.715558310928622</v>
+        <v>1.409343952776863</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.715557452995037</v>
+        <v>1.409343094843278</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.715557681316072</v>
+        <v>1.409343323164313</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.715556885651861</v>
+        <v>1.409342527500101</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.715556947921233</v>
+        <v>1.409342589769474</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.715556975596511</v>
+        <v>1.409342617444751</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.715557127810533</v>
+        <v>1.409342769658774</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.715556781869572</v>
+        <v>1.409342423717813</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.166666627777778</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.715556857976583</v>
+        <v>1.409342499824824</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7499999781250004</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.715557024028245</v>
+        <v>1.409342665876486</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.715557383806845</v>
+        <v>1.409343025655086</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.715557404563303</v>
+        <v>1.409343046411544</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.715557508345591</v>
+        <v>1.409343150193832</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7499999781250004</v>
+        <v>0.1066666677777777</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.715557736666626</v>
+        <v>1.409343378514867</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.715557612127879</v>
+        <v>1.409343253976121</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.715557639803157</v>
+        <v>1.409343281651398</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.09333333222222227</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.715557695153711</v>
+        <v>1.409343337001951</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222227</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.715557958068841</v>
+        <v>1.409343599917082</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.71555787504301</v>
+        <v>1.409343516891251</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.715557667478433</v>
+        <v>1.409343309326674</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.715557681316072</v>
+        <v>1.409343323164313</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.715557819692457</v>
+        <v>1.409343461540698</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.715557536020868</v>
+        <v>1.409343177869109</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.715557363050387</v>
+        <v>1.409343004898628</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.715557259268099</v>
+        <v>1.40934290111634</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.715557404563303</v>
+        <v>1.409343046411544</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7499999781250004</v>
+        <v>0.1066666677777777</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.715557646721976</v>
+        <v>1.409343288570217</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-0.5599999850000004</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.715557473751495</v>
+        <v>1.409343115599736</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.715557176242268</v>
+        <v>1.409342818090509</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.715557162404629</v>
+        <v>1.40934280425287</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.71555679570721</v>
+        <v>1.409342437555451</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.09333333222222227</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.71555679570721</v>
+        <v>1.409342437555451</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7499999781250004</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.715556733437837</v>
+        <v>1.409342375286078</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.715556629655548</v>
+        <v>1.409342271503789</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.715556456685067</v>
+        <v>1.409342098533308</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.715556505116802</v>
+        <v>1.409342146965043</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.715556145338202</v>
+        <v>1.409341787186443</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.715556103825287</v>
+        <v>1.409341745673528</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.715556159175841</v>
+        <v>1.409341801024082</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7499999781250004</v>
+        <v>0.1066666677777777</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.715556214526395</v>
+        <v>1.409341856374636</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7499999781250004</v>
+        <v>-0.5599999850000004</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.71555625603931</v>
+        <v>1.409341897887551</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.71555598620536</v>
+        <v>1.409341628053601</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.09333333222222227</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.715556041555914</v>
+        <v>1.409341683404155</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7499999781250004</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.715556186851118</v>
+        <v>1.409341828699359</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.166666627777778</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.715556152257022</v>
+        <v>1.409341794105262</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.349999978125</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.715556138419383</v>
+        <v>1.409341780267624</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.715556228364033</v>
+        <v>1.409341870212274</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.715556546629718</v>
+        <v>1.409342188477958</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7499999781250004</v>
+        <v>0.1066666677777777</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.715556366740417</v>
+        <v>1.409342008588659</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.715556408253333</v>
+        <v>1.409342050101574</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.715556221445214</v>
+        <v>1.409341863293455</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.715556290633406</v>
+        <v>1.409341932481647</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.715556089987649</v>
+        <v>1.40934173183589</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222231</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.715556131500564</v>
+        <v>1.409341773348805</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.166666627777778</v>
+        <v>0.2399999941666668</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.715556159175841</v>
+        <v>1.409341801024082</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_3_000006.xlsx
+++ b/out/MLP-mamba2_repeat_3_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.5202179551124573</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.2399999941666668</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4870806932449341</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.09333333222222223</v>
+        <v>-0.2300000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4617997407913208</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.1066666677777778</v>
+        <v>0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.5687321424484253</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.09333333222222223</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.2209972441196442</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.53648442029953</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.1066666677777778</v>
+        <v>0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.3508080244064331</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.1066666677777778</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4271804690361023</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4703681766986847</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.2360349893569946</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4765849411487579</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4156659543514252</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.09333333222222223</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.5919738411903381</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.09333333222222223</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.3431344628334045</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.1066666677777778</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.3467332422733307</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5599999850000004</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.3362683057785034</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.1066666677777778</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.5017157793045044</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.1066666677777778</v>
+        <v>0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4798637628555298</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.5640823245048523</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.1066666677777778</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.3742952942848206</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.1066666677777778</v>
+        <v>0.16</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.2477878779172897</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4172289371490479</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3651562929153442</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.09333333222222223</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.599220335483551</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.09333333222222223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.3005096614360809</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.8163770437240601</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.773333320555556</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.5576604008674622</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.4537628293037415</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.1066666677777779</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.312128096818924</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.1066666677777779</v>
+        <v>0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.5204609036445618</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.09333333222222216</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.3501313328742981</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.09333333222222216</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.3320526480674744</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4600467383861542</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.09333333222222209</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.6738080382347107</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.09333333222222212</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.3669983744621277</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.09333333222222212</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.3719099462032318</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.1066666677777779</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.613978385925293</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.1066666677777779</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.3395914435386658</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.1066666677777779</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.418163001537323</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.3</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>0.4438116848468781</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.09333333222222209</v>
+        <v>0.3</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.7761856913566589</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.7733333205555561</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.8838338851928711</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.439999973333334</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.8806725144386292</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.7733333205555561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001887703624767018</v>
+        <v>-0.0001505071560592624</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2429621610111188</v>
+        <v>0.1937144337915407</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>0.2867643237113953</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.1066666677777779</v>
+        <v>0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4863841233024567</v>
+        <v>0.3877954684738684</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.05610994950711986</v>
+        <v>-0.04473662505144678</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.02193151973187923</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.1066666677777779</v>
+        <v>0.16</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1866634411415223</v>
+        <v>0.1488273015840347</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.6688606739044189</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.5733333205555561</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1866634411415223</v>
+        <v>0.1488273015840347</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.7427924275398254</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.7733333205555561</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1864674386832332</v>
+        <v>0.1487550174629798</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.602161941182098</v>
+        <v>0.2220724527183046</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.1754239499568939</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.7733333205555558</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.391990366214386</v>
+        <v>0.5933421210574857</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.115216902493002</v>
+        <v>0.04249106159216588</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.8445990085601807</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.7733333205555558</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.01938349251028</v>
+        <v>0.4559277202391059</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2018131141307353</v>
+        <v>0.07442712414977931</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.5075318813323975</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.307849732197781</v>
+        <v>0.5623117357381268</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1105202053974328</v>
+        <v>0.04075900163180279</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.2796461880207062</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.326903119664346</v>
+        <v>0.5693384631679523</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.04564645436665134</v>
+        <v>0.01683406125898829</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.8385065197944641</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.307559880347741</v>
+        <v>0.5622048559150095</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.05687205544613995</v>
+        <v>0.0209733053068108</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.9091254472732544</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.439999973333334</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.375664804869744</v>
+        <v>0.5873212124477022</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.03424373308407815</v>
+        <v>0.01262836336797664</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.8067361116409302</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.439999973333334</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.387242804413356</v>
+        <v>0.5915902860940718</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.02603534084492132</v>
+        <v>0.009599664042752726</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.7618415951728821</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.439999973333334</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.405053938563369</v>
+        <v>0.5981569335121708</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0115141888911942</v>
+        <v>0.00424317769124753</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.6548299193382263</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.439999973333334</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.402025322933078</v>
+        <v>0.5970368500988474</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.009135495611231592</v>
+        <v>0.003364674982507011</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.6973676681518555</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.439999973333334</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.408778807458894</v>
+        <v>0.5995243225849434</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.004527682237108746</v>
+        <v>0.001665988815887771</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.9604533314704895</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.439999973333334</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.408692910330566</v>
+        <v>0.5994894788253274</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002630735875540364</v>
+        <v>0.0009666730490402668</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.6176886558532715</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.7733333205555558</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.409424305787999</v>
+        <v>0.59975636174072</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001312867937770182</v>
+        <v>0.0004808365245201334</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.02574792504310608</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.09333333222222231</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.409417664953453</v>
+        <v>0.5997507568414505</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0006446704846982648</v>
+        <v>0.000236470445640063</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.2638958990573883</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.409396184603613</v>
+        <v>0.5997396442596696</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0003721547639030092</v>
+        <v>0.0001351814166719149</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.06596069037914276</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.409495945454327</v>
+        <v>0.5997734096240291</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001222222964963988</v>
+        <v>4.187137239341006e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.04709843546152115</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.409364586107127</v>
+        <v>0.5997218561803243</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>5.788215212358921e-05</v>
+        <v>1.745791147271043e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>0.2186843156814575</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.409360295749626</v>
+        <v>0.5997171185196988</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.924674582151908e-05</v>
+        <v>7.230980650542531e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.1324192136526108</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.09333333222222231</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.409361071554305</v>
+        <v>0.5997143102936427</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.159126312874283e-05</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.8017059564590454</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.09333333222222231</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.409354909127283</v>
+        <v>0.5997088447279239</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>6.636802982518164e-06</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.2507843673229218</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.3</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.40935421198188</v>
+        <v>0.599705460109473</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.5050310492515564</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.3</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.409347877121332</v>
+        <v>0.5996997926791993</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.629094660282135</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.409343634511178</v>
+        <v>0.5997001732142569</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.08330200612545013</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.1066666677777777</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.409343862832213</v>
+        <v>0.5997004015352917</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.03087380714714527</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5599999850000004</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.409343952776863</v>
+        <v>0.5997004914799416</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.1838928759098053</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.409343094843278</v>
+        <v>0.5996996335463568</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.05650258436799049</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.409343323164313</v>
+        <v>0.5996998618673915</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.2425962090492249</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.409342527500101</v>
+        <v>0.5996990662031798</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.138508528470993</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.409342589769474</v>
+        <v>0.5996991284725529</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3871164321899414</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.409342617444751</v>
+        <v>0.5996991561478298</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.4516650140285492</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.409342769658774</v>
+        <v>0.599699308361853</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.1585635244846344</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.09333333222222223</v>
+        <v>0.16</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.409342423717813</v>
+        <v>0.5996989624208913</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.5566971898078918</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.1066666677777778</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.409342499824824</v>
+        <v>0.599699038527903</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.2370732724666595</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.409342665876486</v>
+        <v>0.5996992045795645</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.864790141582489</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.409343025655086</v>
+        <v>0.5996995643581645</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.5400833487510681</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.439999973333334</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.409343046411544</v>
+        <v>0.5996995851146223</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.6824790835380554</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.409343150193832</v>
+        <v>0.5996996888969107</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.1654136478900909</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.1066666677777777</v>
+        <v>0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.409343378514867</v>
+        <v>0.5996999172179455</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.1958707720041275</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.409343253976121</v>
+        <v>0.5996997926791993</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3605595231056213</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.09333333222222223</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.409343281651398</v>
+        <v>0.5996998203544761</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.7466374039649963</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.09333333222222227</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.409343337001951</v>
+        <v>0.59969987570503</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.1028157398104668</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.09333333222222227</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.409343599917082</v>
+        <v>0.5997001386201608</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.2750712037086487</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.409343516891251</v>
+        <v>0.5997000555943299</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.3846211731433868</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.409343309326674</v>
+        <v>0.5996998480297532</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4186830222606659</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.409343323164313</v>
+        <v>0.5996998618673915</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.2146643698215485</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.409343461540698</v>
+        <v>0.5997000002437762</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.136034220457077</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.409343177869109</v>
+        <v>0.5996997165721876</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.210965484380722</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.09333333222222223</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.409343004898628</v>
+        <v>0.5996995436017069</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.689417839050293</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.40934290111634</v>
+        <v>0.5996994398194183</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.589589536190033</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.409343046411544</v>
+        <v>0.5996995851146223</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3585681915283203</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.1066666677777777</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.409343288570217</v>
+        <v>0.5996998272732955</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.06778052449226379</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5599999850000004</v>
+        <v>0.16</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.409343115599736</v>
+        <v>0.5996996543028145</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.3360399901866913</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.409342818090509</v>
+        <v>0.5996993567935875</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.05707442387938499</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.40934280425287</v>
+        <v>0.5996993429559491</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3609636723995209</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.09333333222222223</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.409342437555451</v>
+        <v>0.5996989762585299</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.6832712888717651</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.09333333222222227</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.409342437555451</v>
+        <v>0.5996989762585299</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.1117874458432198</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.1066666677777778</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.409342375286078</v>
+        <v>0.5996989139891568</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.1864831298589706</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.409342271503789</v>
+        <v>0.5996988102068682</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.3054998219013214</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.409342098533308</v>
+        <v>0.5996986372363875</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.08946681767702103</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.409342146965043</v>
+        <v>0.599698685668122</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.1491231173276901</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.09333333222222223</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.409341787186443</v>
+        <v>0.599698325889522</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.552348792552948</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.3</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.409341745673528</v>
+        <v>0.5996982843766065</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.5476614832878113</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.3</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.409341801024082</v>
+        <v>0.5996983397271602</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3483521044254303</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.1066666677777777</v>
+        <v>0.3</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.409341856374636</v>
+        <v>0.5996983950777143</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.1899295300245285</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5599999850000004</v>
+        <v>0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.409341897887551</v>
+        <v>0.5996984365906296</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.2830030918121338</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.09333333222222223</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.409341628053601</v>
+        <v>0.5996981667566795</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.693755567073822</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.09333333222222227</v>
+        <v>0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.409341683404155</v>
+        <v>0.5996982221072334</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.3227833807468414</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.409341828699359</v>
+        <v>0.5996983674024374</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.5511934757232666</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.1066666677777778</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.409341794105262</v>
+        <v>0.5996983328083412</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.3329846262931824</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.409341780267624</v>
+        <v>0.5996983189707026</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.9408459663391113</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.409341870212274</v>
+        <v>0.5996984089153528</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.7957649827003479</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.409342188477958</v>
+        <v>0.5996987271810374</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.05407873168587685</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.1066666677777777</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.409342008588659</v>
+        <v>0.5996985472917373</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.1317937523126602</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.409342050101574</v>
+        <v>0.5996985888046527</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4752771258354187</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.409341863293455</v>
+        <v>0.5996984019965333</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.1150376722216606</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.409341932481647</v>
+        <v>0.5996984711847259</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3359039127826691</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.40934173183589</v>
+        <v>0.5996982705389681</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.463937908411026</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.09333333222222231</v>
+        <v>-0.01999999999999991</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.409341773348805</v>
+        <v>0.5996983120518834</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.6136815547943115</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.2399999941666668</v>
+        <v>0.72</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.409341801024082</v>
+        <v>0.5996983397271602</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_3_000006.xlsx
+++ b/out/MLP-mamba2_repeat_3_000006.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.5202179551124573</v>
+        <v>0.5202178955078125</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.1600000000000001</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.4870806932449341</v>
+        <v>0.4870807528495789</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.2300000000000001</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.4617997407913208</v>
+        <v>0.4617998003959656</v>
       </c>
       <c r="JB4" t="n">
         <v>0.3</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.5687321424484253</v>
+        <v>0.5687323212623596</v>
       </c>
       <c r="JB5" t="n">
         <v>0.4399999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.2209972441196442</v>
+        <v>0.2209972888231277</v>
       </c>
       <c r="JB6" t="n">
         <v>0.3</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.3508080244064331</v>
+        <v>0.3508079349994659</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.4399999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.4271804690361023</v>
+        <v>0.4271806478500366</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.4399999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.4703681766986847</v>
+        <v>0.4703683853149414</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.5799999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.2360349893569946</v>
+        <v>0.2360350489616394</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.4399999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.4765849411487579</v>
+        <v>0.476584792137146</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.3</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.4156659543514252</v>
+        <v>0.4156657159328461</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.4399999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.5919738411903381</v>
+        <v>0.5919739007949829</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.4399999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.3431344628334045</v>
+        <v>0.3431343138217926</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.5799999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.3467332422733307</v>
+        <v>0.3467329740524292</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.4399999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.3362683057785034</v>
+        <v>0.3362680673599243</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.5799999999999998</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.5017157793045044</v>
+        <v>0.5017156600952148</v>
       </c>
       <c r="JB18" t="n">
         <v>0.3</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.4798637628555298</v>
+        <v>0.4798638820648193</v>
       </c>
       <c r="JB19" t="n">
         <v>0.3</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.5640823245048523</v>
+        <v>0.5640825629234314</v>
       </c>
       <c r="JB20" t="n">
         <v>0.3</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.3742952942848206</v>
+        <v>0.3742953836917877</v>
       </c>
       <c r="JB21" t="n">
         <v>0.16</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.4172289371490479</v>
+        <v>0.4172287583351135</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.5799999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.3651562929153442</v>
+        <v>0.3651561439037323</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.5799999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.599220335483551</v>
+        <v>0.5992204546928406</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.3</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.3005096614360809</v>
+        <v>0.3005096018314362</v>
       </c>
       <c r="JB26" t="n">
         <v>0.4399999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.8163770437240601</v>
+        <v>0.8163772225379944</v>
       </c>
       <c r="JB27" t="n">
         <v>0.5799999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.5576604008674622</v>
+        <v>0.5576618313789368</v>
       </c>
       <c r="JB28" t="n">
         <v>0.3</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.4537628293037415</v>
+        <v>0.4537636935710907</v>
       </c>
       <c r="JB29" t="n">
         <v>0.5799999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.312128096818924</v>
+        <v>0.3121283352375031</v>
       </c>
       <c r="JB30" t="n">
         <v>0.3</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.5204609036445618</v>
+        <v>0.5204612016677856</v>
       </c>
       <c r="JB31" t="n">
         <v>0.02000000000000007</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.3501313328742981</v>
+        <v>0.3501313030719757</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.4399999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.3320526480674744</v>
+        <v>0.3320524096488953</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.1600000000000001</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.6738080382347107</v>
+        <v>0.6738089323043823</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.4399999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.3669983744621277</v>
+        <v>0.3669987618923187</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.1600000000000001</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.3719099462032318</v>
+        <v>0.3719102442264557</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.4399999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.613978385925293</v>
+        <v>0.6139789819717407</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.7199999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.3395914435386658</v>
+        <v>0.3395916521549225</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.5799999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.418163001537323</v>
+        <v>0.4181632697582245</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.3</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.4438116848468781</v>
+        <v>0.4438124001026154</v>
       </c>
       <c r="JB41" t="n">
         <v>0.3</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.7761856913566589</v>
+        <v>0.7761867046356201</v>
       </c>
       <c r="JB42" t="n">
         <v>0.5799999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.8838338851928711</v>
+        <v>0.8838330507278442</v>
       </c>
       <c r="JB43" t="n">
         <v>0.5799999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.8806725144386292</v>
+        <v>0.8806710839271545</v>
       </c>
       <c r="JB44" t="n">
         <v>0.4399999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.2867643237113953</v>
+        <v>0.2867644727230072</v>
       </c>
       <c r="JB45" t="n">
         <v>0.3</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.02193151973187923</v>
+        <v>0.02193191275000572</v>
       </c>
       <c r="JB46" t="n">
         <v>0.16</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.6688606739044189</v>
+        <v>0.6688588857650757</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.7199999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.7427924275398254</v>
+        <v>0.7427905201911926</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.4399999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.1754239499568939</v>
+        <v>0.175423726439476</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.1600000000000001</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.8445990085601807</v>
+        <v>0.8445974588394165</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.3</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.5075318813323975</v>
+        <v>0.5075291395187378</v>
       </c>
       <c r="JB51" t="n">
         <v>0.4399999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.2796461880207062</v>
+        <v>0.2796463966369629</v>
       </c>
       <c r="JB52" t="n">
         <v>0.7199999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.8385065197944641</v>
+        <v>0.8385052680969238</v>
       </c>
       <c r="JB53" t="n">
         <v>0.5799999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.9091254472732544</v>
+        <v>0.9091240167617798</v>
       </c>
       <c r="JB54" t="n">
         <v>0.5799999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.8067361116409302</v>
+        <v>0.8067357540130615</v>
       </c>
       <c r="JB55" t="n">
         <v>0.8599999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.7618415951728821</v>
+        <v>0.7618379592895508</v>
       </c>
       <c r="JB56" t="n">
         <v>0.7199999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.6548299193382263</v>
+        <v>0.6548305749893188</v>
       </c>
       <c r="JB57" t="n">
         <v>0.7199999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.6973676681518555</v>
+        <v>0.6973686218261719</v>
       </c>
       <c r="JB58" t="n">
         <v>0.7199999999999999</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.9604533314704895</v>
+        <v>0.9604523181915283</v>
       </c>
       <c r="JB59" t="n">
         <v>0.4399999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.6176886558532715</v>
+        <v>0.6176846027374268</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.4399999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.02574792504310608</v>
+        <v>0.02574803866446018</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.5799999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.2638958990573883</v>
+        <v>0.2638960480690002</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.8599999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.06596069037914276</v>
+        <v>0.06596077978610992</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.04709843546152115</v>
+        <v>0.04709860682487488</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.2186843156814575</v>
+        <v>0.2186843603849411</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.7199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.1324192136526108</v>
+        <v>0.1324195116758347</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.7199999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.8017059564590454</v>
+        <v>0.8017057180404663</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.5799999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.2507843673229218</v>
+        <v>0.2507845163345337</v>
       </c>
       <c r="JB68" t="n">
         <v>0.3</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.5050310492515564</v>
+        <v>0.5050315260887146</v>
       </c>
       <c r="JB69" t="n">
         <v>0.3</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.629094660282135</v>
+        <v>0.6290943026542664</v>
       </c>
       <c r="JB70" t="n">
         <v>0.02000000000000007</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.08330200612545013</v>
+        <v>0.08330229669809341</v>
       </c>
       <c r="JB71" t="n">
         <v>0.02000000000000007</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.03087380714714527</v>
+        <v>0.03087391890585423</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.1199999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.1838928759098053</v>
+        <v>0.1838935613632202</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.05650258436799049</v>
+        <v>0.05650279298424721</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.2425962090492249</v>
+        <v>0.2425962388515472</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.138508528470993</v>
+        <v>0.1385089308023453</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.7199999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.3871164321899414</v>
+        <v>0.3871168196201324</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.7199999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.4516650140285492</v>
+        <v>0.4516653120517731</v>
       </c>
       <c r="JB78" t="n">
         <v>0.1600000000000001</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.1585635244846344</v>
+        <v>0.1585638672113419</v>
       </c>
       <c r="JB79" t="n">
         <v>0.16</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.5566971898078918</v>
+        <v>0.5566974878311157</v>
       </c>
       <c r="JB80" t="n">
         <v>0.4399999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.2370732724666595</v>
+        <v>0.237073689699173</v>
       </c>
       <c r="JB81" t="n">
         <v>0.4399999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.864790141582489</v>
+        <v>0.8647899627685547</v>
       </c>
       <c r="JB82" t="n">
         <v>0.7199999999999999</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.5400833487510681</v>
+        <v>0.5400828719139099</v>
       </c>
       <c r="JB83" t="n">
         <v>0.4399999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.6824790835380554</v>
+        <v>0.6824788451194763</v>
       </c>
       <c r="JB84" t="n">
         <v>0.4399999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.1654136478900909</v>
+        <v>0.1654141545295715</v>
       </c>
       <c r="JB85" t="n">
         <v>0.3</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.1958707720041275</v>
+        <v>0.1958711594343185</v>
       </c>
       <c r="JB86" t="n">
         <v>0.3</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.3605595231056213</v>
+        <v>0.3605603575706482</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.5799999999999998</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.7466374039649963</v>
+        <v>0.7466373443603516</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.5799999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.1028157398104668</v>
+        <v>0.1028160974383354</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.2750712037086487</v>
+        <v>0.2750717103481293</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.1600000000000001</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.3846211731433868</v>
+        <v>0.3846220076084137</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.4399999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.4186830222606659</v>
+        <v>0.4186837673187256</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.4399999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.2146643698215485</v>
+        <v>0.2146649062633514</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.4399999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.136034220457077</v>
+        <v>0.1360347121953964</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.4399999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.210965484380722</v>
+        <v>0.210966169834137</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.4399999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.689417839050293</v>
+        <v>0.6894182562828064</v>
       </c>
       <c r="JB96" t="n">
         <v>0.3</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.589589536190033</v>
+        <v>0.5895901322364807</v>
       </c>
       <c r="JB97" t="n">
         <v>0.3</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.3585681915283203</v>
+        <v>0.3585689663887024</v>
       </c>
       <c r="JB98" t="n">
         <v>0.4399999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.06778052449226379</v>
+        <v>0.06778086721897125</v>
       </c>
       <c r="JB99" t="n">
         <v>0.16</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.3360399901866913</v>
+        <v>0.3360410630702972</v>
       </c>
       <c r="JB100" t="n">
         <v>0.02000000000000007</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.05707442387938499</v>
+        <v>0.05707467719912529</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.4399999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.3609636723995209</v>
+        <v>0.3609646260738373</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.4399999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.6832712888717651</v>
+        <v>0.6832717061042786</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.5799999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.1117874458432198</v>
+        <v>0.1117875576019287</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.5799999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.1864831298589706</v>
+        <v>0.1864836663007736</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.7199999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.3054998219013214</v>
+        <v>0.3055005967617035</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.08946681767702103</v>
+        <v>0.08946701139211655</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.1491231173276901</v>
+        <v>0.1491229981184006</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.4399999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.552348792552948</v>
+        <v>0.5523490309715271</v>
       </c>
       <c r="JB109" t="n">
         <v>0.3</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.5476614832878113</v>
+        <v>0.5476614236831665</v>
       </c>
       <c r="JB110" t="n">
         <v>0.3</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.3483521044254303</v>
+        <v>0.348352313041687</v>
       </c>
       <c r="JB111" t="n">
         <v>0.3</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.1899295300245285</v>
+        <v>0.1899299323558807</v>
       </c>
       <c r="JB112" t="n">
         <v>0.3</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.2830030918121338</v>
+        <v>0.2830033004283905</v>
       </c>
       <c r="JB113" t="n">
         <v>0.16</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.693755567073822</v>
+        <v>0.6937558650970459</v>
       </c>
       <c r="JB114" t="n">
         <v>0.3</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.3227833807468414</v>
+        <v>0.322783887386322</v>
       </c>
       <c r="JB115" t="n">
         <v>0.4399999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.5511934757232666</v>
+        <v>0.5511938333511353</v>
       </c>
       <c r="JB116" t="n">
         <v>0.7199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.3329846262931824</v>
+        <v>0.3329850733280182</v>
       </c>
       <c r="JB117" t="n">
         <v>0.7199999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.9408459663391113</v>
+        <v>0.9408461451530457</v>
       </c>
       <c r="JB118" t="n">
         <v>0.5799999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.7957649827003479</v>
+        <v>0.7957645058631897</v>
       </c>
       <c r="JB119" t="n">
         <v>0.3</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.05407873168587685</v>
+        <v>0.05407888814806938</v>
       </c>
       <c r="JB120" t="n">
         <v>0.4399999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.1317937523126602</v>
+        <v>0.131793811917305</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.4399999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.4752771258354187</v>
+        <v>0.4752771854400635</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.7199999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.1150376722216606</v>
+        <v>0.1150379925966263</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.4399999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.3359039127826691</v>
+        <v>0.3359039723873138</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.1600000000000001</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.463937908411026</v>
+        <v>0.4639382660388947</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.01999999999999991</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.6136815547943115</v>
+        <v>0.6136817336082458</v>
       </c>
       <c r="JB126" t="n">
         <v>0.72</v>
